--- a/SWYNEX_Task_1_Data_Cleaning.xlsx
+++ b/SWYNEX_Task_1_Data_Cleaning.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6c24732fd6fface/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6c24732fd6fface/Documents/Downloads/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0215383-D51D-44B6-81F5-6DF2266EB926}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7355059B-E5D6-43DE-BDC4-C87C167D9D98}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -786,6 +797,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4917,7 +4932,7 @@
       <c r="I51" t="s">
         <v>16</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="2">
         <v>9999</v>
       </c>
       <c r="K51">
@@ -5254,6 +5269,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K61" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <conditionalFormatting sqref="J51">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/SWYNEX_Task_1_Data_Cleaning.xlsx
+++ b/SWYNEX_Task_1_Data_Cleaning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6c24732fd6fface/Documents/Downloads/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6c24732fd6fface/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7355059B-E5D6-43DE-BDC4-C87C167D9D98}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0878597-54B6-4A99-94CF-A3FEEED92EE9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1091,14 +1091,16 @@
   <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="16" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -3095,7 +3097,7 @@
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" customWidth="1"/>
     <col min="5" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>

--- a/SWYNEX_Task_1_Data_Cleaning.xlsx
+++ b/SWYNEX_Task_1_Data_Cleaning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6c24732fd6fface/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0878597-54B6-4A99-94CF-A3FEEED92EE9}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{3FC8E352-8CEF-4B31-933E-18AF2FC7EBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E7B7667-5C67-45C1-B1CC-B749CC020043}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -4935,7 +4935,7 @@
         <v>16</v>
       </c>
       <c r="J51" s="2">
-        <v>9999</v>
+        <v>5000</v>
       </c>
       <c r="K51">
         <f t="shared" si="0"/>
